--- a/data/processed/positivacao/2024-09_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2024-09_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -26089,7 +26089,7 @@
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B991" t="inlineStr"/>
@@ -37441,7 +37441,7 @@
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1428" t="inlineStr"/>
@@ -65865,7 +65865,7 @@
     <row r="2522">
       <c r="A2522" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2522" t="inlineStr"/>
@@ -67562,12 +67562,12 @@
       <c r="A2588" t="inlineStr"/>
       <c r="B2588" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 6 cliente(s), não positivou 85 cliente(s) - Total vendido: R$ 7.114,81
+          <t>Vendedor 1 - VENDEDOR 01: positivou 6 cliente(s), não positivou 85 cliente(s) - Total vendido: R$ 7.114,81
 Vendedor 18 - LOJA: positivou 183 cliente(s), não positivou 707 cliente(s) - Total vendido: R$ 76.617,57
-Vendedor 3 - FERNANDA: positivou 108 cliente(s), não positivou 328 cliente(s) - Total vendido: R$ 174.062,90
-Vendedor 4 - DANIELA: positivou 111 cliente(s), não positivou 537 cliente(s) - Total vendido: R$ 59.781,75
+Vendedor 3 - VENDEDOR 03: positivou 108 cliente(s), não positivou 328 cliente(s) - Total vendido: R$ 174.062,90
+Vendedor 4 - VENDEDOR 04: positivou 111 cliente(s), não positivou 537 cliente(s) - Total vendido: R$ 59.781,75
 Vendedor 5 - SITE: positivou 5 cliente(s), não positivou 439 cliente(s) - Total vendido: R$ 1.014,93
-Vendedor 8 - RAFAEL: positivou 3 cliente(s), não positivou 61 cliente(s) - Total vendido: R$ 424,50</t>
+Vendedor 8 - VENDEDOR 08: positivou 3 cliente(s), não positivou 61 cliente(s) - Total vendido: R$ 424,50</t>
         </is>
       </c>
       <c r="C2588" t="inlineStr"/>
